--- a/youzi/92科比/index.xlsx
+++ b/youzi/92科比/index.xlsx
@@ -39,121 +39,271 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F8538"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF52B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,79 +315,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF52B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C5C9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,79 +417,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,162 +489,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -513,6 +513,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -525,18 +543,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
@@ -549,61 +573,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -627,19 +621,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>603488</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -564.96万</v>
       </c>
       <c r="E2">
@@ -2041,37 +2041,37 @@
       <c r="H2">
         <v>-0.82</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="13">
         <v>10.89</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="9">
         <v>2.01</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="3">
         <v>-0.12</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="10">
         <v>-4.5</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="11">
         <v>-4.73</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="4">
         <v>-6.27</v>
       </c>
       <c r="O2" s="5">
         <v>-5.56</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="1">
         <v>-9.11</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="6">
         <v>-8.52</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="12">
         <v>-7.1</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="7">
         <v>-7.81</v>
       </c>
       <c r="T2" s="8">
@@ -2103,37 +2103,37 @@
       <c r="H3">
         <v>0.15</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="17">
         <v>-10.15</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="22">
         <v>-1.15</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="25">
         <v>-4.11</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="18">
         <v>-8.56</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="23">
         <v>-7.11</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="26">
         <v>-8.59</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="14">
         <v>0.56</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="19">
         <v>10.63</v>
       </c>
       <c r="Q3" s="15">
         <v>21.7</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="24">
         <v>31.48</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="16">
         <v>32.59</v>
       </c>
       <c r="T3" s="20">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>301329</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -1373.82万</v>
       </c>
       <c r="E4">
@@ -2165,40 +2165,40 @@
       <c r="H4">
         <v>-1.77</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="31">
         <v>4.75</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="39">
         <v>5.48</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="32">
         <v>1.1</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="35">
         <v>-7.94</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="36">
         <v>-9.62</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="37">
         <v>-8.22</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="27">
         <v>-0.65</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="28">
         <v>-2.33</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="34">
         <v>-2.58</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="33">
         <v>-1.1</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="29">
         <v>-2.82</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="38">
         <v>-4.01</v>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>002119</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 476.88万</v>
       </c>
       <c r="E5">
@@ -2227,40 +2227,40 @@
       <c r="H5">
         <v>5.4</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="41">
         <v>1.95</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="47">
         <v>3.82</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="42">
         <v>8.03</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="43">
         <v>2.04</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="44">
         <v>1.61</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="49">
         <v>-2.3</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="50">
         <v>7.47</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="51">
         <v>18.24</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="48">
         <v>11.2</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="52">
         <v>14.29</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="45">
         <v>7.64</v>
       </c>
-      <c r="T5" s="42">
+      <c r="T5" s="40">
         <v>1.82</v>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>002119</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -6443.67万</v>
       </c>
       <c r="E6">
@@ -2289,40 +2289,40 @@
       <c r="H6">
         <v>-1.75</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="55">
         <v>3.64</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="56">
         <v>7.85</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="61">
         <v>1.86</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="62">
         <v>1.43</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="64">
         <v>-2.47</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="57">
         <v>7.28</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="58">
         <v>18.03</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="65">
         <v>11.01</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="59">
         <v>14.09</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="53">
         <v>7.46</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="54">
         <v>11.75</v>
       </c>
-      <c r="T6" s="53">
+      <c r="T6" s="60">
         <v>1.65</v>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>301128</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 6396.32万</v>
       </c>
       <c r="E7">
@@ -2351,37 +2351,37 @@
       <c r="H7">
         <v>-0.12</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="74">
         <v>20.14</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="69">
         <v>24.98</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="76">
         <v>22.53</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="70">
         <v>16.38</v>
       </c>
       <c r="M7" s="66">
         <v>23.75</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="71">
         <v>28.83</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="72">
         <v>30.75</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="77">
         <v>26.96</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="78">
         <v>25.24</v>
       </c>
       <c r="R7" s="73">
         <v>36.79</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="67">
         <v>41.68</v>
       </c>
       <c r="T7" s="68">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="87">
+      <c r="I9" s="90">
         <v>83.33</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="86">
         <v>83.33</v>
       </c>
       <c r="K9" s="79">
         <v>66.67</v>
       </c>
-      <c r="L9" s="80">
+      <c r="L9" s="83">
         <v>50</v>
       </c>
-      <c r="M9" s="89">
+      <c r="M9" s="80">
         <v>33.33</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="81">
         <v>33.33</v>
       </c>
-      <c r="O9" s="81">
+      <c r="O9" s="87">
         <v>66.67</v>
       </c>
-      <c r="P9" s="84">
+      <c r="P9" s="88">
         <v>66.67</v>
       </c>
-      <c r="Q9" s="85">
+      <c r="Q9" s="82">
         <v>66.67</v>
       </c>
-      <c r="R9" s="86">
+      <c r="R9" s="89">
         <v>66.67</v>
       </c>
-      <c r="S9" s="82">
+      <c r="S9" s="84">
         <v>66.67</v>
       </c>
-      <c r="T9" s="83">
+      <c r="T9" s="85">
         <v>83.33</v>
       </c>
     </row>
@@ -2495,40 +2495,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="102">
+      <c r="I10" s="92">
         <v>5.2</v>
       </c>
-      <c r="J10" s="96">
+      <c r="J10" s="93">
         <v>7.16</v>
       </c>
-      <c r="K10" s="97">
+      <c r="K10" s="100">
         <v>4.88</v>
       </c>
-      <c r="L10" s="98">
+      <c r="L10" s="97">
         <v>-0.19</v>
       </c>
-      <c r="M10" s="99">
+      <c r="M10" s="94">
         <v>0.24</v>
       </c>
-      <c r="N10" s="100">
+      <c r="N10" s="101">
         <v>1.79</v>
       </c>
-      <c r="O10" s="92">
+      <c r="O10" s="102">
         <v>8.43</v>
       </c>
-      <c r="P10" s="93">
+      <c r="P10" s="98">
         <v>9.23</v>
       </c>
-      <c r="Q10" s="101">
+      <c r="Q10" s="99">
         <v>10.19</v>
       </c>
-      <c r="R10" s="94">
+      <c r="R10" s="91">
         <v>13.64</v>
       </c>
-      <c r="S10" s="95">
+      <c r="S10" s="96">
         <v>13.84</v>
       </c>
-      <c r="T10" s="91">
+      <c r="T10" s="95">
         <v>65.27</v>
       </c>
     </row>

--- a/youzi/92科比/index.xlsx
+++ b/youzi/92科比/index.xlsx
@@ -39,6 +39,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1B7632"/>
         <bgColor/>
       </patternFill>
@@ -51,6 +75,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF9FCFA"/>
         <bgColor/>
       </patternFill>
@@ -63,43 +111,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1D7D34"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,36 +147,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7C34"/>
         <bgColor/>
       </patternFill>
@@ -153,12 +183,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -171,25 +195,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,6 +231,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF52B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF85CD96"/>
         <bgColor/>
       </patternFill>
@@ -225,49 +273,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF52B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,19 +339,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
+        <fgColor rgb="FFE46470"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,7 +351,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,193 +447,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -513,25 +525,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -543,18 +567,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
@@ -567,7 +579,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -615,37 +627,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6ED"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>603488</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -564.96万</v>
       </c>
       <c r="E2">
@@ -2041,37 +2041,37 @@
       <c r="H2">
         <v>-0.82</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="9">
         <v>10.89</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="3">
         <v>2.01</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="11">
         <v>-0.12</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="4">
         <v>-4.5</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="7">
         <v>-4.73</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="12">
         <v>-6.27</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="10">
         <v>-5.56</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="5">
         <v>-9.11</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="13">
         <v>-8.52</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="1">
         <v>-7.1</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="2">
         <v>-7.81</v>
       </c>
       <c r="T2" s="8">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>603256</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 2245.44万</v>
       </c>
       <c r="E3">
@@ -2103,40 +2103,40 @@
       <c r="H3">
         <v>0.15</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="19">
         <v>-10.15</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="26">
         <v>-1.15</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="20">
         <v>-4.11</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="17">
         <v>-8.56</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="18">
         <v>-7.11</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="23">
         <v>-8.59</v>
       </c>
       <c r="O3" s="14">
         <v>0.56</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="15">
         <v>10.63</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="16">
         <v>21.7</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="21">
         <v>31.48</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="22">
         <v>32.59</v>
       </c>
-      <c r="T3" s="20">
+      <c r="T3" s="24">
         <v>290</v>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>301329</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -1373.82万</v>
       </c>
       <c r="E4">
@@ -2165,40 +2165,40 @@
       <c r="H4">
         <v>-1.77</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="39">
         <v>4.75</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="34">
         <v>5.48</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="29">
         <v>1.1</v>
       </c>
       <c r="L4" s="35">
         <v>-7.94</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="30">
         <v>-9.62</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="36">
         <v>-8.22</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="31">
         <v>-0.65</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="32">
         <v>-2.33</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="27">
         <v>-2.58</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="28">
         <v>-1.1</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="37">
         <v>-2.82</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="33">
         <v>-4.01</v>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>002119</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 476.88万</v>
       </c>
       <c r="E5">
@@ -2230,37 +2230,37 @@
       <c r="I5" s="41">
         <v>1.95</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="51">
         <v>3.82</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="48">
         <v>8.03</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="49">
         <v>2.04</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="52">
         <v>1.61</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="42">
         <v>-2.3</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="46">
         <v>7.47</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="43">
         <v>18.24</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="44">
         <v>11.2</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="47">
         <v>14.29</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="40">
         <v>7.64</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="50">
         <v>1.82</v>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>002119</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -6443.67万</v>
       </c>
       <c r="E6">
@@ -2289,40 +2289,40 @@
       <c r="H6">
         <v>-1.75</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="65">
         <v>3.64</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="57">
         <v>7.85</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="63">
         <v>1.86</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="64">
         <v>1.43</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="53">
         <v>-2.47</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="54">
         <v>7.28</v>
       </c>
       <c r="O6" s="58">
         <v>18.03</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="55">
         <v>11.01</v>
       </c>
       <c r="Q6" s="59">
         <v>14.09</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="61">
         <v>7.46</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="60">
         <v>11.75</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="62">
         <v>1.65</v>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>301128</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="68" t="str">
         <v>净买: 6396.32万</v>
       </c>
       <c r="E7">
@@ -2351,40 +2351,40 @@
       <c r="H7">
         <v>-0.12</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="69">
         <v>20.14</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="70">
         <v>24.98</v>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="78">
         <v>22.53</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="71">
         <v>16.38</v>
       </c>
       <c r="M7" s="66">
         <v>23.75</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="67">
         <v>28.83</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="75">
         <v>30.75</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="72">
         <v>26.96</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="76">
         <v>25.24</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="77">
         <v>36.79</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="73">
         <v>41.68</v>
       </c>
-      <c r="T7" s="68">
+      <c r="T7" s="74">
         <v>69.65</v>
       </c>
     </row>
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="90">
+      <c r="I9" s="83">
         <v>83.33</v>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="87">
         <v>83.33</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="84">
         <v>66.67</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="79">
         <v>50</v>
       </c>
-      <c r="M9" s="80">
+      <c r="M9" s="85">
         <v>33.33</v>
       </c>
-      <c r="N9" s="81">
+      <c r="N9" s="80">
         <v>33.33</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="89">
         <v>66.67</v>
       </c>
-      <c r="P9" s="88">
+      <c r="P9" s="90">
         <v>66.67</v>
       </c>
-      <c r="Q9" s="82">
+      <c r="Q9" s="88">
         <v>66.67</v>
       </c>
-      <c r="R9" s="89">
+      <c r="R9" s="86">
         <v>66.67</v>
       </c>
-      <c r="S9" s="84">
+      <c r="S9" s="81">
         <v>66.67</v>
       </c>
-      <c r="T9" s="85">
+      <c r="T9" s="82">
         <v>83.33</v>
       </c>
     </row>
@@ -2495,40 +2495,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="92">
+      <c r="I10" s="99">
         <v>5.2</v>
       </c>
-      <c r="J10" s="93">
+      <c r="J10" s="95">
         <v>7.16</v>
       </c>
       <c r="K10" s="100">
         <v>4.88</v>
       </c>
-      <c r="L10" s="97">
+      <c r="L10" s="101">
         <v>-0.19</v>
       </c>
-      <c r="M10" s="94">
+      <c r="M10" s="96">
         <v>0.24</v>
       </c>
-      <c r="N10" s="101">
+      <c r="N10" s="102">
         <v>1.79</v>
       </c>
-      <c r="O10" s="102">
+      <c r="O10" s="97">
         <v>8.43</v>
       </c>
-      <c r="P10" s="98">
+      <c r="P10" s="91">
         <v>9.23</v>
       </c>
-      <c r="Q10" s="99">
+      <c r="Q10" s="92">
         <v>10.19</v>
       </c>
-      <c r="R10" s="91">
+      <c r="R10" s="98">
         <v>13.64</v>
       </c>
-      <c r="S10" s="96">
+      <c r="S10" s="93">
         <v>13.84</v>
       </c>
-      <c r="T10" s="95">
+      <c r="T10" s="94">
         <v>65.27</v>
       </c>
     </row>

--- a/youzi/92科比/index.xlsx
+++ b/youzi/92科比/index.xlsx
@@ -39,31 +39,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF218E3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F8538"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,109 +213,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,73 +315,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF52B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,25 +387,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,204 +507,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -519,6 +519,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
@@ -531,24 +537,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
@@ -579,31 +573,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -615,6 +585,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -640,12 +646,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>603488</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -564.96万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.82</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="11">
         <v>10.89</v>
       </c>
       <c r="J2" s="3">
         <v>2.01</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="4">
         <v>-0.12</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="8">
         <v>-4.5</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="5">
         <v>-4.73</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="9">
         <v>-6.27</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="12">
         <v>-5.56</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="6">
         <v>-9.11</v>
       </c>
       <c r="Q2" s="13">
         <v>-8.52</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="7">
         <v>-7.1</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="10">
         <v>-7.81</v>
       </c>
-      <c r="T2" s="8">
-        <v>32.54</v>
+      <c r="T2" s="1">
+        <v>33.25</v>
       </c>
     </row>
     <row r="3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0.15</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="26">
         <v>-10.15</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="19">
         <v>-1.15</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="14">
         <v>-4.11</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="20">
         <v>-8.56</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="21">
         <v>-7.11</v>
       </c>
       <c r="N3" s="23">
         <v>-8.59</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="17">
         <v>0.56</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="24">
         <v>10.63</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="15">
         <v>21.7</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="18">
         <v>31.48</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="16">
         <v>32.59</v>
       </c>
-      <c r="T3" s="24">
-        <v>290</v>
+      <c r="T3" s="22">
+        <v>285.04</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>301329</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -1373.82万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.77</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="35">
         <v>4.75</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="30">
         <v>5.48</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="27">
         <v>1.1</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="28">
         <v>-7.94</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="31">
         <v>-9.62</v>
       </c>
       <c r="N4" s="36">
         <v>-8.22</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="32">
         <v>-0.65</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="33">
         <v>-2.33</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="38">
         <v>-2.58</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="34">
         <v>-1.1</v>
       </c>
       <c r="S4" s="37">
         <v>-2.82</v>
       </c>
-      <c r="T4" s="33">
-        <v>-4.01</v>
+      <c r="T4" s="39">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>002119</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 476.88万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>5.4</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="40">
         <v>1.95</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="49">
         <v>3.82</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="43">
         <v>8.03</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="44">
         <v>2.04</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="50">
         <v>1.61</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="47">
         <v>-2.3</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="41">
         <v>7.47</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="42">
         <v>18.24</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="51">
         <v>11.2</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="52">
         <v>14.29</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="48">
         <v>7.64</v>
       </c>
-      <c r="T5" s="50">
-        <v>1.82</v>
+      <c r="T5" s="45">
+        <v>-3.82</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>002119</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -6443.67万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>-1.75</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="63">
         <v>3.64</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="55">
         <v>7.85</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="56">
         <v>1.86</v>
       </c>
       <c r="L6" s="64">
         <v>1.43</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="57">
         <v>-2.47</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="59">
         <v>7.28</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="65">
         <v>18.03</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="60">
         <v>11.01</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="53">
         <v>14.09</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="54">
         <v>7.46</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="61">
         <v>11.75</v>
       </c>
       <c r="T6" s="62">
-        <v>1.65</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>301128</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="78" t="str">
         <v>净买: 6396.32万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-0.12</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="70">
         <v>20.14</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="71">
         <v>24.98</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="66">
         <v>22.53</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="74">
         <v>16.38</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="75">
         <v>23.75</v>
       </c>
       <c r="N7" s="67">
         <v>28.83</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="76">
         <v>30.75</v>
       </c>
       <c r="P7" s="72">
         <v>26.96</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="68">
         <v>25.24</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="69">
         <v>36.79</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="77">
         <v>41.68</v>
       </c>
-      <c r="T7" s="74">
-        <v>69.65</v>
+      <c r="T7" s="73">
+        <v>70.84</v>
       </c>
     </row>
     <row r="8">
@@ -2447,41 +2447,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="83">
+      <c r="I9" s="86">
         <v>83.33</v>
       </c>
-      <c r="J9" s="87">
+      <c r="J9" s="83">
         <v>83.33</v>
       </c>
-      <c r="K9" s="84">
+      <c r="K9" s="87">
         <v>66.67</v>
       </c>
-      <c r="L9" s="79">
+      <c r="L9" s="90">
         <v>50</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="80">
         <v>33.33</v>
       </c>
-      <c r="N9" s="80">
+      <c r="N9" s="81">
         <v>33.33</v>
       </c>
-      <c r="O9" s="89">
+      <c r="O9" s="84">
         <v>66.67</v>
       </c>
-      <c r="P9" s="90">
+      <c r="P9" s="88">
         <v>66.67</v>
       </c>
-      <c r="Q9" s="88">
+      <c r="Q9" s="85">
         <v>66.67</v>
       </c>
-      <c r="R9" s="86">
+      <c r="R9" s="89">
         <v>66.67</v>
       </c>
-      <c r="S9" s="81">
+      <c r="S9" s="82">
         <v>66.67</v>
       </c>
-      <c r="T9" s="82">
-        <v>83.33</v>
+      <c r="T9" s="79">
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="99">
+      <c r="I10" s="101">
         <v>5.2</v>
       </c>
-      <c r="J10" s="95">
+      <c r="J10" s="93">
         <v>7.16</v>
       </c>
-      <c r="K10" s="100">
+      <c r="K10" s="96">
         <v>4.88</v>
       </c>
-      <c r="L10" s="101">
+      <c r="L10" s="102">
         <v>-0.19</v>
       </c>
-      <c r="M10" s="96">
+      <c r="M10" s="91">
         <v>0.24</v>
       </c>
-      <c r="N10" s="102">
+      <c r="N10" s="92">
         <v>1.79</v>
       </c>
       <c r="O10" s="97">
         <v>8.43</v>
       </c>
-      <c r="P10" s="91">
+      <c r="P10" s="94">
         <v>9.23</v>
       </c>
-      <c r="Q10" s="92">
+      <c r="Q10" s="98">
         <v>10.19</v>
       </c>
-      <c r="R10" s="98">
+      <c r="R10" s="95">
         <v>13.64</v>
       </c>
-      <c r="S10" s="93">
+      <c r="S10" s="99">
         <v>13.84</v>
       </c>
-      <c r="T10" s="94">
-        <v>65.27</v>
+      <c r="T10" s="100">
+        <v>63.1</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/92科比/index.xlsx
+++ b/youzi/92科比/index.xlsx
@@ -39,6 +39,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -51,25 +63,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0ADB4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,55 +135,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1D7C34"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,7 +153,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,19 +165,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +195,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,6 +237,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -219,12 +255,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE3F3E6"/>
         <bgColor/>
       </patternFill>
@@ -237,37 +267,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,31 +285,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,193 +489,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -519,7 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,12 +561,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
@@ -549,31 +573,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -585,6 +591,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDF4A58"/>
         <bgColor/>
       </patternFill>
@@ -604,48 +646,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>603488</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -564.96万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.82</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="5">
         <v>10.89</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="12">
         <v>2.01</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="6">
         <v>-0.12</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="13">
         <v>-4.5</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="7">
         <v>-4.73</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="11">
         <v>-6.27</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="8">
         <v>-5.56</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="10">
         <v>-9.11</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="1">
         <v>-8.52</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="2">
         <v>-7.1</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="9">
         <v>-7.81</v>
       </c>
-      <c r="T2" s="1">
-        <v>33.25</v>
+      <c r="T2" s="3">
+        <v>33.61</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>603256</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 2245.44万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0.15</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="20">
         <v>-10.15</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="14">
         <v>-1.15</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="15">
         <v>-4.11</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="21">
         <v>-8.56</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="16">
         <v>-7.11</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="17">
         <v>-8.59</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="18">
         <v>0.56</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="22">
         <v>10.63</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="23">
         <v>21.7</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="24">
         <v>31.48</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="25">
         <v>32.59</v>
       </c>
-      <c r="T3" s="22">
-        <v>285.04</v>
+      <c r="T3" s="19">
+        <v>294.15</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>301329</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -1373.82万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.77</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="27">
         <v>4.75</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="36">
         <v>5.48</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="32">
         <v>1.1</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="33">
         <v>-7.94</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="28">
         <v>-9.62</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="30">
         <v>-8.22</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="37">
         <v>-0.65</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="38">
         <v>-2.33</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="31">
         <v>-2.58</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="29">
         <v>-1.1</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="34">
         <v>-2.82</v>
       </c>
       <c r="T4" s="39">
-        <v>-2.74</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>002119</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 476.88万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>5.4</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="41">
         <v>1.95</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="51">
         <v>3.82</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="46">
         <v>8.03</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="52">
         <v>2.04</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="47">
         <v>1.61</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="44">
         <v>-2.3</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="40">
         <v>7.47</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="48">
         <v>18.24</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="42">
         <v>11.2</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="49">
         <v>14.29</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="50">
         <v>7.64</v>
       </c>
-      <c r="T5" s="45">
-        <v>-3.82</v>
+      <c r="T5" s="43">
+        <v>-5.6</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>002119</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="54" t="str">
         <v>净卖: -6443.67万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>-1.75</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="60">
         <v>3.64</v>
       </c>
       <c r="J6" s="55">
         <v>7.85</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="61">
         <v>1.86</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="56">
         <v>1.43</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="65">
         <v>-2.47</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="57">
         <v>7.28</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="58">
         <v>18.03</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="62">
         <v>11.01</v>
       </c>
       <c r="Q6" s="53">
         <v>14.09</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="64">
         <v>7.46</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="63">
         <v>11.75</v>
       </c>
-      <c r="T6" s="62">
-        <v>-3.99</v>
+      <c r="T6" s="59">
+        <v>-5.77</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>301128</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 6396.32万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-0.12</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="69">
         <v>20.14</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="70">
         <v>24.98</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="71">
         <v>22.53</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="76">
         <v>16.38</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="77">
         <v>23.75</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="78">
         <v>28.83</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="66">
         <v>30.75</v>
       </c>
       <c r="P7" s="72">
         <v>26.96</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="67">
         <v>25.24</v>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="73">
         <v>36.79</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="68">
         <v>41.68</v>
       </c>
-      <c r="T7" s="73">
-        <v>70.84</v>
+      <c r="T7" s="74">
+        <v>63.92</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="86">
+      <c r="I9" s="79">
         <v>83.33</v>
       </c>
       <c r="J9" s="83">
         <v>83.33</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="80">
         <v>66.67</v>
       </c>
-      <c r="L9" s="90">
+      <c r="L9" s="84">
         <v>50</v>
       </c>
-      <c r="M9" s="80">
+      <c r="M9" s="81">
         <v>33.33</v>
       </c>
-      <c r="N9" s="81">
+      <c r="N9" s="85">
         <v>33.33</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="82">
         <v>66.67</v>
       </c>
       <c r="P9" s="88">
         <v>66.67</v>
       </c>
-      <c r="Q9" s="85">
+      <c r="Q9" s="89">
         <v>66.67</v>
       </c>
-      <c r="R9" s="89">
+      <c r="R9" s="90">
         <v>66.67</v>
       </c>
-      <c r="S9" s="82">
+      <c r="S9" s="87">
         <v>66.67</v>
       </c>
-      <c r="T9" s="79">
+      <c r="T9" s="86">
         <v>50</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="101">
+      <c r="I10" s="91">
         <v>5.2</v>
       </c>
-      <c r="J10" s="93">
+      <c r="J10" s="101">
         <v>7.16</v>
       </c>
-      <c r="K10" s="96">
+      <c r="K10" s="102">
         <v>4.88</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="98">
         <v>-0.19</v>
       </c>
-      <c r="M10" s="91">
+      <c r="M10" s="92">
         <v>0.24</v>
       </c>
-      <c r="N10" s="92">
+      <c r="N10" s="99">
         <v>1.79</v>
       </c>
-      <c r="O10" s="97">
+      <c r="O10" s="96">
         <v>8.43</v>
       </c>
-      <c r="P10" s="94">
+      <c r="P10" s="93">
         <v>9.23</v>
       </c>
-      <c r="Q10" s="98">
+      <c r="Q10" s="94">
         <v>10.19</v>
       </c>
-      <c r="R10" s="95">
+      <c r="R10" s="97">
         <v>13.64</v>
       </c>
-      <c r="S10" s="99">
+      <c r="S10" s="100">
         <v>13.84</v>
       </c>
-      <c r="T10" s="100">
-        <v>63.1</v>
+      <c r="T10" s="95">
+        <v>62.98</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/92科比/index.xlsx
+++ b/youzi/92科比/index.xlsx
@@ -39,19 +39,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7D34"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF218E3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,91 +243,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36AC51"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,85 +291,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,25 +357,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,25 +423,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,205 +507,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -519,61 +525,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -609,18 +615,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6ED"/>
         <bgColor/>
       </patternFill>
@@ -628,6 +622,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>603488</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -564.96万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.82</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="1">
         <v>10.89</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="2">
         <v>2.01</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="12">
         <v>-0.12</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="4">
         <v>-4.5</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="5">
         <v>-4.73</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="9">
         <v>-6.27</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="13">
         <v>-5.56</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="6">
         <v>-9.11</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="10">
         <v>-8.52</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="7">
         <v>-7.1</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="3">
         <v>-7.81</v>
       </c>
-      <c r="T2" s="3">
-        <v>33.61</v>
+      <c r="T2" s="8">
+        <v>27.22</v>
       </c>
     </row>
     <row r="3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0.15</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="24">
         <v>-10.15</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="25">
         <v>-1.15</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="22">
         <v>-4.11</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="23">
         <v>-8.56</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="19">
         <v>-7.11</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="20">
         <v>-8.59</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="14">
         <v>0.56</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="15">
         <v>10.63</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="16">
         <v>21.7</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="21">
         <v>31.48</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="17">
         <v>32.59</v>
       </c>
-      <c r="T3" s="19">
-        <v>294.15</v>
+      <c r="T3" s="18">
+        <v>296.3</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>301329</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="34" t="str">
         <v>净卖: -1373.82万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.77</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="35">
         <v>4.75</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="32">
         <v>5.48</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="38">
         <v>1.1</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="27">
         <v>-7.94</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="33">
         <v>-9.62</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="36">
         <v>-8.22</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="28">
         <v>-0.65</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="29">
         <v>-2.33</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="30">
         <v>-2.58</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="31">
         <v>-1.1</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="39">
         <v>-2.82</v>
       </c>
-      <c r="T4" s="39">
-        <v>-2.45</v>
+      <c r="T4" s="37">
+        <v>-4.66</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>002119</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 476.88万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>5.4</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="49">
         <v>1.95</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="44">
         <v>3.82</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="45">
         <v>8.03</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="51">
         <v>2.04</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="52">
         <v>1.61</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="46">
         <v>-2.3</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="47">
         <v>7.47</v>
       </c>
       <c r="P5" s="48">
         <v>18.24</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="40">
         <v>11.2</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="50">
         <v>14.29</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="41">
         <v>7.64</v>
       </c>
-      <c r="T5" s="43">
-        <v>-5.6</v>
+      <c r="T5" s="42">
+        <v>-10.38</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>002119</v>
       </c>
-      <c r="D6" s="54" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -6443.67万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>-1.75</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="61">
         <v>3.64</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="57">
         <v>7.85</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="54">
         <v>1.86</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="58">
         <v>1.43</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="59">
         <v>-2.47</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="60">
         <v>7.28</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="63">
         <v>18.03</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="55">
         <v>11.01</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="56">
         <v>14.09</v>
       </c>
       <c r="R6" s="64">
         <v>7.46</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="62">
         <v>11.75</v>
       </c>
-      <c r="T6" s="59">
-        <v>-5.77</v>
+      <c r="T6" s="65">
+        <v>-10.53</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>301128</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="78" t="str">
         <v>净买: 6396.32万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-0.12</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="70">
         <v>20.14</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="74">
         <v>24.98</v>
       </c>
       <c r="K7" s="71">
         <v>22.53</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="66">
         <v>16.38</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="67">
         <v>23.75</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="72">
         <v>28.83</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="68">
         <v>30.75</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="73">
         <v>26.96</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="69">
         <v>25.24</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="77">
         <v>36.79</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="75">
         <v>41.68</v>
       </c>
-      <c r="T7" s="74">
-        <v>63.92</v>
+      <c r="T7" s="76">
+        <v>74.69</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="79">
+      <c r="I9" s="90">
         <v>83.33</v>
       </c>
-      <c r="J9" s="83">
+      <c r="J9" s="79">
         <v>83.33</v>
       </c>
-      <c r="K9" s="80">
+      <c r="K9" s="86">
         <v>66.67</v>
       </c>
-      <c r="L9" s="84">
+      <c r="L9" s="83">
         <v>50</v>
       </c>
-      <c r="M9" s="81">
+      <c r="M9" s="89">
         <v>33.33</v>
       </c>
-      <c r="N9" s="85">
+      <c r="N9" s="80">
         <v>33.33</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="84">
         <v>66.67</v>
       </c>
-      <c r="P9" s="88">
+      <c r="P9" s="87">
         <v>66.67</v>
       </c>
-      <c r="Q9" s="89">
+      <c r="Q9" s="81">
         <v>66.67</v>
       </c>
-      <c r="R9" s="90">
+      <c r="R9" s="88">
         <v>66.67</v>
       </c>
-      <c r="S9" s="87">
+      <c r="S9" s="82">
         <v>66.67</v>
       </c>
-      <c r="T9" s="86">
+      <c r="T9" s="85">
         <v>50</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="91">
+      <c r="I10" s="100">
         <v>5.2</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="96">
         <v>7.16</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="92">
         <v>4.88</v>
       </c>
-      <c r="L10" s="98">
+      <c r="L10" s="97">
         <v>-0.19</v>
       </c>
-      <c r="M10" s="92">
+      <c r="M10" s="93">
         <v>0.24</v>
       </c>
-      <c r="N10" s="99">
+      <c r="N10" s="98">
         <v>1.79</v>
       </c>
-      <c r="O10" s="96">
+      <c r="O10" s="94">
         <v>8.43</v>
       </c>
-      <c r="P10" s="93">
+      <c r="P10" s="99">
         <v>9.23</v>
       </c>
-      <c r="Q10" s="94">
+      <c r="Q10" s="101">
         <v>10.19</v>
       </c>
-      <c r="R10" s="97">
+      <c r="R10" s="102">
         <v>13.64</v>
       </c>
-      <c r="S10" s="100">
+      <c r="S10" s="95">
         <v>13.84</v>
       </c>
-      <c r="T10" s="95">
-        <v>62.98</v>
+      <c r="T10" s="91">
+        <v>62.11</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/92科比/index.xlsx
+++ b/youzi/92科比/index.xlsx
@@ -39,31 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0ADB4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F8538"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
+        <fgColor rgb="FF26A042"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,25 +105,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF218E3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,85 +231,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,43 +333,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,49 +375,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF36AC51"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,211 +477,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -519,49 +567,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -579,7 +585,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -610,18 +622,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>603488</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -564.96万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.82</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="13">
         <v>10.89</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>2.01</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="2">
         <v>-0.12</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>-4.5</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="7">
         <v>-4.73</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="8">
         <v>-6.27</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="10">
         <v>-5.56</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="11">
         <v>-9.11</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="4">
         <v>-8.52</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="5">
         <v>-7.1</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="9">
         <v>-7.81</v>
       </c>
-      <c r="T2" s="8">
-        <v>27.22</v>
+      <c r="T2" s="12">
+        <v>35.86</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>603256</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="14" t="str">
         <v>净买: 2245.44万</v>
       </c>
       <c r="E3">
@@ -2103,16 +2103,16 @@
       <c r="H3">
         <v>0.15</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="15">
         <v>-10.15</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="16">
         <v>-1.15</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="23">
         <v>-4.11</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="17">
         <v>-8.56</v>
       </c>
       <c r="M3" s="19">
@@ -2121,23 +2121,23 @@
       <c r="N3" s="20">
         <v>-8.59</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="21">
         <v>0.56</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="22">
         <v>10.63</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="24">
         <v>21.7</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="25">
         <v>31.48</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="18">
         <v>32.59</v>
       </c>
-      <c r="T3" s="18">
-        <v>296.3</v>
+      <c r="T3" s="26">
+        <v>294.11</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>301329</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="32" t="str">
         <v>净卖: -1373.82万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.77</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="39">
         <v>4.75</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="33">
         <v>5.48</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="27">
         <v>1.1</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="37">
         <v>-7.94</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="34">
         <v>-9.62</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="28">
         <v>-8.22</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="35">
         <v>-0.65</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="38">
         <v>-2.33</v>
       </c>
       <c r="Q4" s="30">
         <v>-2.58</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="36">
         <v>-1.1</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="29">
         <v>-2.82</v>
       </c>
-      <c r="T4" s="37">
-        <v>-4.66</v>
+      <c r="T4" s="31">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>002119</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="49" t="str">
         <v>净买: 476.88万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>5.4</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="50">
         <v>1.95</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="46">
         <v>3.82</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="51">
         <v>8.03</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="43">
         <v>2.04</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="47">
         <v>1.61</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="52">
         <v>-2.3</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="40">
         <v>7.47</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="44">
         <v>18.24</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="48">
         <v>11.2</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="42">
         <v>14.29</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="45">
         <v>7.64</v>
       </c>
-      <c r="T5" s="42">
-        <v>-10.38</v>
+      <c r="T5" s="41">
+        <v>-8.77</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>002119</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -6443.67万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>-1.75</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="57">
         <v>3.64</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="58">
         <v>7.85</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="61">
         <v>1.86</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="62">
         <v>1.43</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="54">
         <v>-2.47</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="55">
         <v>7.28</v>
       </c>
       <c r="O6" s="63">
         <v>18.03</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="64">
         <v>11.01</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="65">
         <v>14.09</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="59">
         <v>7.46</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="60">
         <v>11.75</v>
       </c>
-      <c r="T6" s="65">
-        <v>-10.53</v>
+      <c r="T6" s="53">
+        <v>-8.93</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>301128</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 6396.32万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-0.12</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="66">
         <v>20.14</v>
       </c>
       <c r="J7" s="74">
         <v>24.98</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="70">
         <v>22.53</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="67">
         <v>16.38</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="71">
         <v>23.75</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="68">
         <v>28.83</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="75">
         <v>30.75</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="72">
         <v>26.96</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="76">
         <v>25.24</v>
       </c>
       <c r="R7" s="77">
         <v>36.79</v>
       </c>
-      <c r="S7" s="75">
+      <c r="S7" s="69">
         <v>41.68</v>
       </c>
-      <c r="T7" s="76">
-        <v>74.69</v>
+      <c r="T7" s="78">
+        <v>67.61</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="90">
+      <c r="I9" s="87">
         <v>83.33</v>
       </c>
-      <c r="J9" s="79">
+      <c r="J9" s="89">
         <v>83.33</v>
       </c>
-      <c r="K9" s="86">
+      <c r="K9" s="82">
         <v>66.67</v>
       </c>
       <c r="L9" s="83">
         <v>50</v>
       </c>
-      <c r="M9" s="89">
+      <c r="M9" s="88">
         <v>33.33</v>
       </c>
-      <c r="N9" s="80">
+      <c r="N9" s="90">
         <v>33.33</v>
       </c>
       <c r="O9" s="84">
         <v>66.67</v>
       </c>
-      <c r="P9" s="87">
+      <c r="P9" s="85">
         <v>66.67</v>
       </c>
-      <c r="Q9" s="81">
+      <c r="Q9" s="79">
         <v>66.67</v>
       </c>
-      <c r="R9" s="88">
+      <c r="R9" s="80">
         <v>66.67</v>
       </c>
-      <c r="S9" s="82">
+      <c r="S9" s="86">
         <v>66.67</v>
       </c>
-      <c r="T9" s="85">
+      <c r="T9" s="81">
         <v>50</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="100">
+      <c r="I10" s="98">
         <v>5.2</v>
       </c>
-      <c r="J10" s="96">
+      <c r="J10" s="102">
         <v>7.16</v>
       </c>
-      <c r="K10" s="92">
+      <c r="K10" s="91">
         <v>4.88</v>
       </c>
-      <c r="L10" s="97">
+      <c r="L10" s="92">
         <v>-0.19</v>
       </c>
-      <c r="M10" s="93">
+      <c r="M10" s="95">
         <v>0.24</v>
       </c>
-      <c r="N10" s="98">
+      <c r="N10" s="93">
         <v>1.79</v>
       </c>
-      <c r="O10" s="94">
+      <c r="O10" s="99">
         <v>8.43</v>
       </c>
-      <c r="P10" s="99">
+      <c r="P10" s="94">
         <v>9.23</v>
       </c>
-      <c r="Q10" s="101">
+      <c r="Q10" s="100">
         <v>10.19</v>
       </c>
-      <c r="R10" s="102">
+      <c r="R10" s="101">
         <v>13.64</v>
       </c>
-      <c r="S10" s="95">
+      <c r="S10" s="96">
         <v>13.84</v>
       </c>
-      <c r="T10" s="91">
-        <v>62.11</v>
+      <c r="T10" s="97">
+        <v>62.77</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/92科比/index.xlsx
+++ b/youzi/92科比/index.xlsx
@@ -39,24 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0ADB4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1D7D34"/>
         <bgColor/>
       </patternFill>
@@ -69,49 +99,211 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,199 +315,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,174 +501,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -513,18 +513,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
@@ -543,48 +561,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6ED"/>
         <bgColor/>
       </patternFill>
@@ -603,31 +597,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>603488</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="7" t="str">
         <v>净卖: -564.96万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.82</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>10.89</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="8">
         <v>2.01</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <v>-0.12</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>-4.5</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="12">
         <v>-4.73</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="3">
         <v>-6.27</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="4">
         <v>-5.56</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="13">
         <v>-9.11</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="9">
         <v>-8.52</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="10">
         <v>-7.1</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="6">
         <v>-7.81</v>
       </c>
-      <c r="T2" s="12">
-        <v>35.86</v>
+      <c r="T2" s="5">
+        <v>29.7</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>603256</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="18" t="str">
         <v>净买: 2245.44万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0.15</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="19">
         <v>-10.15</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="22">
         <v>-1.15</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="15">
         <v>-4.11</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="23">
         <v>-8.56</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="24">
         <v>-7.11</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="16">
         <v>-8.59</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="25">
         <v>0.56</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="20">
         <v>10.63</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="17">
         <v>21.7</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="26">
         <v>31.48</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="14">
         <v>32.59</v>
       </c>
-      <c r="T3" s="26">
-        <v>294.11</v>
+      <c r="T3" s="21">
+        <v>306.11</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>301329</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -1373.82万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.77</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="36">
         <v>4.75</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="38">
         <v>5.48</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="31">
         <v>1.1</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="39">
         <v>-7.94</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="32">
         <v>-9.62</v>
       </c>
       <c r="N4" s="28">
         <v>-8.22</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="29">
         <v>-0.65</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="33">
         <v>-2.33</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="27">
         <v>-2.58</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="34">
         <v>-1.1</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="37">
         <v>-2.82</v>
       </c>
-      <c r="T4" s="31">
-        <v>-3.27</v>
+      <c r="T4" s="35">
+        <v>-4.87</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>002119</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 476.88万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>5.4</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="40">
         <v>1.95</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="49">
         <v>3.82</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="47">
         <v>8.03</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="50">
         <v>2.04</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="51">
         <v>1.61</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="43">
         <v>-2.3</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="52">
         <v>7.47</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="41">
         <v>18.24</v>
       </c>
       <c r="Q5" s="48">
         <v>11.2</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="44">
         <v>14.29</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="42">
         <v>7.64</v>
       </c>
-      <c r="T5" s="41">
-        <v>-8.77</v>
+      <c r="T5" s="45">
+        <v>-10.07</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>002119</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -6443.67万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>-1.75</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="65">
         <v>3.64</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="57">
         <v>7.85</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="53">
         <v>1.86</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="61">
         <v>1.43</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="58">
         <v>-2.47</v>
       </c>
-      <c r="N6" s="55">
+      <c r="N6" s="62">
         <v>7.28</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="54">
         <v>18.03</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="63">
         <v>11.01</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="55">
         <v>14.09</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="56">
         <v>7.46</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="59">
         <v>11.75</v>
       </c>
-      <c r="T6" s="53">
-        <v>-8.93</v>
+      <c r="T6" s="64">
+        <v>-10.23</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>301128</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="77" t="str">
         <v>净买: 6396.32万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-0.12</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="71">
         <v>20.14</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="78">
         <v>24.98</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="72">
         <v>22.53</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="73">
         <v>16.38</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="68">
         <v>23.75</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="69">
         <v>28.83</v>
       </c>
       <c r="O7" s="75">
         <v>30.75</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="76">
         <v>26.96</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="70">
         <v>25.24</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="66">
         <v>36.79</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="74">
         <v>41.68</v>
       </c>
-      <c r="T7" s="78">
-        <v>67.61</v>
+      <c r="T7" s="67">
+        <v>66.75</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="87">
+      <c r="I9" s="84">
         <v>83.33</v>
       </c>
-      <c r="J9" s="89">
+      <c r="J9" s="88">
         <v>83.33</v>
       </c>
-      <c r="K9" s="82">
+      <c r="K9" s="85">
         <v>66.67</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="86">
         <v>50</v>
       </c>
-      <c r="M9" s="88">
+      <c r="M9" s="80">
         <v>33.33</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="89">
         <v>33.33</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="87">
         <v>66.67</v>
       </c>
-      <c r="P9" s="85">
+      <c r="P9" s="90">
         <v>66.67</v>
       </c>
-      <c r="Q9" s="79">
+      <c r="Q9" s="81">
         <v>66.67</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="82">
         <v>66.67</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="79">
         <v>66.67</v>
       </c>
-      <c r="T9" s="81">
+      <c r="T9" s="83">
         <v>50</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="98">
+      <c r="I10" s="101">
         <v>5.2</v>
       </c>
       <c r="J10" s="102">
         <v>7.16</v>
       </c>
-      <c r="K10" s="91">
+      <c r="K10" s="96">
         <v>4.88</v>
       </c>
-      <c r="L10" s="92">
+      <c r="L10" s="91">
         <v>-0.19</v>
       </c>
-      <c r="M10" s="95">
+      <c r="M10" s="99">
         <v>0.24</v>
       </c>
-      <c r="N10" s="93">
+      <c r="N10" s="92">
         <v>1.79</v>
       </c>
-      <c r="O10" s="99">
+      <c r="O10" s="93">
         <v>8.43</v>
       </c>
       <c r="P10" s="94">
         <v>9.23</v>
       </c>
-      <c r="Q10" s="100">
+      <c r="Q10" s="95">
         <v>10.19</v>
       </c>
-      <c r="R10" s="101">
+      <c r="R10" s="98">
         <v>13.64</v>
       </c>
-      <c r="S10" s="96">
+      <c r="S10" s="97">
         <v>13.84</v>
       </c>
-      <c r="T10" s="97">
-        <v>62.77</v>
+      <c r="T10" s="100">
+        <v>62.9</v>
       </c>
     </row>
   </sheetData>
